--- a/data/age-regression/groups.xlsx
+++ b/data/age-regression/groups.xlsx
@@ -1,32 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\EpImAge\data\age-regression\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EpInflammAge\data\age-regression\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADDE93E-C10B-46AD-8BF4-9D3C8376786C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C7BEC6-D44F-482B-A6C2-1FC362BB6905}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35040" yWindow="3080" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18270" yWindow="2340" windowWidth="19695" windowHeight="18150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$66</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="268">
   <si>
     <t>ICD-11 chapter</t>
   </si>
@@ -796,13 +792,55 @@
   </si>
   <si>
     <t>This work 16</t>
+  </si>
+  <si>
+    <t>ICD-11 name</t>
+  </si>
+  <si>
+    <t>Infections</t>
+  </si>
+  <si>
+    <t>Neoplasms</t>
+  </si>
+  <si>
+    <t>Immune</t>
+  </si>
+  <si>
+    <t>Endocrine</t>
+  </si>
+  <si>
+    <t>Mental</t>
+  </si>
+  <si>
+    <t>Nervous</t>
+  </si>
+  <si>
+    <t>Circulatory </t>
+  </si>
+  <si>
+    <t>Respiratory</t>
+  </si>
+  <si>
+    <t>Digestive</t>
+  </si>
+  <si>
+    <t>Developmental</t>
+  </si>
+  <si>
+    <t>COVID-19</t>
+  </si>
+  <si>
+    <t>Skeletal</t>
+  </si>
+  <si>
+    <t>Urinary</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -814,6 +852,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -877,9 +921,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -917,9 +961,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -952,9 +996,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -987,9 +1048,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1163,21 +1241,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I66"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J66"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="128.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="108.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="128.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="108.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>90</v>
       </c>
@@ -1188,25 +1267,28 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>97</v>
       </c>
@@ -1217,25 +1299,28 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E2" t="s">
         <v>76</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>135</v>
       </c>
-      <c r="F2" t="s">
-        <v>165</v>
-      </c>
       <c r="G2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H2" t="s">
         <v>89</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>98</v>
       </c>
@@ -1246,25 +1331,28 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E3" t="s">
         <v>76</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>135</v>
       </c>
-      <c r="F3" t="s">
-        <v>165</v>
-      </c>
       <c r="G3" t="s">
+        <v>165</v>
+      </c>
+      <c r="H3" t="s">
         <v>89</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>96</v>
       </c>
@@ -1275,25 +1363,28 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
+        <v>255</v>
+      </c>
+      <c r="E4" t="s">
         <v>76</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>135</v>
       </c>
-      <c r="F4" t="s">
-        <v>165</v>
-      </c>
       <c r="G4" t="s">
+        <v>165</v>
+      </c>
+      <c r="H4" t="s">
         <v>89</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>94</v>
       </c>
@@ -1304,25 +1395,28 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
+        <v>255</v>
+      </c>
+      <c r="E5" t="s">
         <v>57</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>134</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>166</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>147</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>91</v>
       </c>
@@ -1333,25 +1427,28 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
+        <v>255</v>
+      </c>
+      <c r="E6" t="s">
         <v>57</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>132</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>164</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>146</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>93</v>
       </c>
@@ -1362,25 +1459,28 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
+        <v>255</v>
+      </c>
+      <c r="E7" t="s">
         <v>57</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>133</v>
       </c>
-      <c r="F7" t="s">
-        <v>165</v>
-      </c>
       <c r="G7" t="s">
+        <v>165</v>
+      </c>
+      <c r="H7" t="s">
         <v>80</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>95</v>
       </c>
@@ -1391,25 +1491,28 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
+        <v>255</v>
+      </c>
+      <c r="E8" t="s">
         <v>57</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>133</v>
       </c>
-      <c r="F8" t="s">
-        <v>165</v>
-      </c>
       <c r="G8" t="s">
+        <v>165</v>
+      </c>
+      <c r="H8" t="s">
         <v>80</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>92</v>
       </c>
@@ -1420,25 +1523,28 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
+        <v>255</v>
+      </c>
+      <c r="E9" t="s">
         <v>57</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>133</v>
       </c>
-      <c r="F9" t="s">
-        <v>165</v>
-      </c>
       <c r="G9" t="s">
+        <v>165</v>
+      </c>
+      <c r="H9" t="s">
         <v>80</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>141</v>
       </c>
@@ -1449,25 +1555,28 @@
         <v>2</v>
       </c>
       <c r="D10" t="s">
+        <v>256</v>
+      </c>
+      <c r="E10" t="s">
         <v>137</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>150</v>
       </c>
-      <c r="F10" t="s">
-        <v>165</v>
-      </c>
       <c r="G10" t="s">
+        <v>165</v>
+      </c>
+      <c r="H10" t="s">
         <v>151</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>143</v>
       </c>
@@ -1478,25 +1587,28 @@
         <v>2</v>
       </c>
       <c r="D11" t="s">
+        <v>256</v>
+      </c>
+      <c r="E11" t="s">
         <v>139</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>154</v>
       </c>
-      <c r="F11" t="s">
-        <v>165</v>
-      </c>
       <c r="G11" t="s">
+        <v>165</v>
+      </c>
+      <c r="H11" t="s">
         <v>155</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>142</v>
       </c>
@@ -1507,25 +1619,28 @@
         <v>2</v>
       </c>
       <c r="D12" t="s">
+        <v>256</v>
+      </c>
+      <c r="E12" t="s">
         <v>138</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>152</v>
       </c>
-      <c r="F12" t="s">
-        <v>165</v>
-      </c>
       <c r="G12" t="s">
+        <v>165</v>
+      </c>
+      <c r="H12" t="s">
         <v>153</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>140</v>
       </c>
@@ -1536,25 +1651,28 @@
         <v>2</v>
       </c>
       <c r="D13" t="s">
+        <v>256</v>
+      </c>
+      <c r="E13" t="s">
         <v>136</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>148</v>
       </c>
-      <c r="F13" t="s">
-        <v>165</v>
-      </c>
       <c r="G13" t="s">
+        <v>165</v>
+      </c>
+      <c r="H13" t="s">
         <v>149</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>113</v>
       </c>
@@ -1565,25 +1683,28 @@
         <v>4</v>
       </c>
       <c r="D14" t="s">
+        <v>257</v>
+      </c>
+      <c r="E14" t="s">
         <v>68</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>156</v>
       </c>
-      <c r="F14" t="s">
-        <v>165</v>
-      </c>
       <c r="G14" t="s">
+        <v>165</v>
+      </c>
+      <c r="H14" t="s">
         <v>157</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>1</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>114</v>
       </c>
@@ -1594,25 +1715,28 @@
         <v>4</v>
       </c>
       <c r="D15" t="s">
+        <v>257</v>
+      </c>
+      <c r="E15" t="s">
         <v>69</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>161</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>164</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>162</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>1</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>117</v>
       </c>
@@ -1623,25 +1747,28 @@
         <v>5</v>
       </c>
       <c r="D16" t="s">
+        <v>258</v>
+      </c>
+      <c r="E16" t="s">
         <v>70</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>167</v>
       </c>
-      <c r="F16" t="s">
-        <v>165</v>
-      </c>
       <c r="G16" t="s">
+        <v>165</v>
+      </c>
+      <c r="H16" t="s">
         <v>84</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
       </c>
       <c r="I16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>115</v>
       </c>
@@ -1652,25 +1779,28 @@
         <v>5</v>
       </c>
       <c r="D17" t="s">
+        <v>258</v>
+      </c>
+      <c r="E17" t="s">
         <v>63</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>158</v>
       </c>
-      <c r="F17" t="s">
-        <v>165</v>
-      </c>
       <c r="G17" t="s">
+        <v>165</v>
+      </c>
+      <c r="H17" t="s">
         <v>159</v>
-      </c>
-      <c r="H17">
-        <v>1</v>
       </c>
       <c r="I17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>118</v>
       </c>
@@ -1681,25 +1811,28 @@
         <v>5</v>
       </c>
       <c r="D18" t="s">
+        <v>258</v>
+      </c>
+      <c r="E18" t="s">
         <v>72</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>168</v>
       </c>
-      <c r="F18" t="s">
-        <v>165</v>
-      </c>
       <c r="G18" t="s">
+        <v>165</v>
+      </c>
+      <c r="H18" t="s">
         <v>87</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
       </c>
       <c r="I18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>227</v>
       </c>
@@ -1710,25 +1843,28 @@
         <v>5</v>
       </c>
       <c r="D19" t="s">
+        <v>258</v>
+      </c>
+      <c r="E19" t="s">
         <v>229</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>233</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>217</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>231</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
       </c>
       <c r="I19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>119</v>
       </c>
@@ -1739,25 +1875,28 @@
         <v>5</v>
       </c>
       <c r="D20" t="s">
+        <v>258</v>
+      </c>
+      <c r="E20" t="s">
         <v>67</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>160</v>
       </c>
-      <c r="F20" t="s">
-        <v>165</v>
-      </c>
       <c r="G20" t="s">
+        <v>165</v>
+      </c>
+      <c r="H20" t="s">
         <v>83</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>120</v>
       </c>
@@ -1768,25 +1907,28 @@
         <v>5</v>
       </c>
       <c r="D21" t="s">
+        <v>258</v>
+      </c>
+      <c r="E21" t="s">
         <v>67</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>160</v>
       </c>
-      <c r="F21" t="s">
-        <v>165</v>
-      </c>
       <c r="G21" t="s">
+        <v>165</v>
+      </c>
+      <c r="H21" t="s">
         <v>83</v>
-      </c>
-      <c r="H21">
-        <v>1</v>
       </c>
       <c r="I21">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>116</v>
       </c>
@@ -1797,25 +1939,28 @@
         <v>5</v>
       </c>
       <c r="D22" t="s">
+        <v>258</v>
+      </c>
+      <c r="E22" t="s">
         <v>67</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>160</v>
       </c>
-      <c r="F22" t="s">
-        <v>165</v>
-      </c>
       <c r="G22" t="s">
+        <v>165</v>
+      </c>
+      <c r="H22" t="s">
         <v>83</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
       </c>
       <c r="I22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>172</v>
       </c>
@@ -1826,25 +1971,28 @@
         <v>6</v>
       </c>
       <c r="D23" t="s">
+        <v>259</v>
+      </c>
+      <c r="E23" t="s">
         <v>60</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>174</v>
       </c>
-      <c r="F23" t="s">
-        <v>165</v>
-      </c>
       <c r="G23" t="s">
+        <v>165</v>
+      </c>
+      <c r="H23" t="s">
         <v>79</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>2</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>123</v>
       </c>
@@ -1855,25 +2003,28 @@
         <v>6</v>
       </c>
       <c r="D24" t="s">
+        <v>259</v>
+      </c>
+      <c r="E24" t="s">
         <v>60</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>174</v>
       </c>
-      <c r="F24" t="s">
-        <v>165</v>
-      </c>
       <c r="G24" t="s">
+        <v>165</v>
+      </c>
+      <c r="H24" t="s">
         <v>79</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>2</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>125</v>
       </c>
@@ -1884,25 +2035,28 @@
         <v>6</v>
       </c>
       <c r="D25" t="s">
+        <v>259</v>
+      </c>
+      <c r="E25" t="s">
         <v>60</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>174</v>
       </c>
-      <c r="F25" t="s">
-        <v>165</v>
-      </c>
       <c r="G25" t="s">
+        <v>165</v>
+      </c>
+      <c r="H25" t="s">
         <v>79</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <v>2</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>173</v>
       </c>
@@ -1913,25 +2067,28 @@
         <v>6</v>
       </c>
       <c r="D26" t="s">
+        <v>259</v>
+      </c>
+      <c r="E26" t="s">
         <v>171</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>176</v>
       </c>
-      <c r="F26" t="s">
-        <v>165</v>
-      </c>
       <c r="G26" t="s">
+        <v>165</v>
+      </c>
+      <c r="H26" t="s">
         <v>175</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>2</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>122</v>
       </c>
@@ -1942,25 +2099,28 @@
         <v>6</v>
       </c>
       <c r="D27" t="s">
+        <v>259</v>
+      </c>
+      <c r="E27" t="s">
         <v>56</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>170</v>
       </c>
-      <c r="F27" t="s">
-        <v>165</v>
-      </c>
       <c r="G27" t="s">
+        <v>165</v>
+      </c>
+      <c r="H27" t="s">
         <v>78</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <v>2</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>124</v>
       </c>
@@ -1971,25 +2131,28 @@
         <v>6</v>
       </c>
       <c r="D28" t="s">
+        <v>259</v>
+      </c>
+      <c r="E28" t="s">
         <v>56</v>
       </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>177</v>
       </c>
-      <c r="F28" t="s">
-        <v>165</v>
-      </c>
       <c r="G28" t="s">
+        <v>165</v>
+      </c>
+      <c r="H28" t="s">
         <v>178</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <v>2</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>121</v>
       </c>
@@ -2000,25 +2163,28 @@
         <v>6</v>
       </c>
       <c r="D29" t="s">
+        <v>259</v>
+      </c>
+      <c r="E29" t="s">
         <v>54</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>169</v>
       </c>
-      <c r="F29" t="s">
-        <v>165</v>
-      </c>
       <c r="G29" t="s">
+        <v>165</v>
+      </c>
+      <c r="H29" t="s">
         <v>77</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>2</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>236</v>
       </c>
@@ -2029,25 +2195,28 @@
         <v>6</v>
       </c>
       <c r="D30" t="s">
+        <v>259</v>
+      </c>
+      <c r="E30" t="s">
         <v>235</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>238</v>
       </c>
-      <c r="F30" t="s">
-        <v>165</v>
-      </c>
       <c r="G30" t="s">
+        <v>165</v>
+      </c>
+      <c r="H30" t="s">
         <v>239</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <v>2</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>241</v>
       </c>
@@ -2058,25 +2227,28 @@
         <v>6</v>
       </c>
       <c r="D31" t="s">
+        <v>259</v>
+      </c>
+      <c r="E31" t="s">
         <v>240</v>
       </c>
-      <c r="E31" t="s">
+      <c r="F31" t="s">
         <v>246</v>
       </c>
-      <c r="F31" t="s">
-        <v>165</v>
-      </c>
       <c r="G31" t="s">
+        <v>165</v>
+      </c>
+      <c r="H31" t="s">
         <v>243</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <v>2</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>126</v>
       </c>
@@ -2087,25 +2259,28 @@
         <v>8</v>
       </c>
       <c r="D32" t="s">
+        <v>260</v>
+      </c>
+      <c r="E32" t="s">
         <v>59</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>179</v>
       </c>
-      <c r="F32" t="s">
-        <v>165</v>
-      </c>
       <c r="G32" t="s">
+        <v>165</v>
+      </c>
+      <c r="H32" t="s">
         <v>180</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <v>3</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>130</v>
       </c>
@@ -2116,25 +2291,28 @@
         <v>8</v>
       </c>
       <c r="D33" t="s">
+        <v>260</v>
+      </c>
+      <c r="E33" t="s">
         <v>59</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>179</v>
       </c>
-      <c r="F33" t="s">
-        <v>165</v>
-      </c>
       <c r="G33" t="s">
+        <v>165</v>
+      </c>
+      <c r="H33" t="s">
         <v>180</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <v>3</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>245</v>
       </c>
@@ -2145,25 +2323,28 @@
         <v>8</v>
       </c>
       <c r="D34" t="s">
+        <v>260</v>
+      </c>
+      <c r="E34" t="s">
         <v>244</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>248</v>
       </c>
-      <c r="F34" t="s">
-        <v>165</v>
-      </c>
       <c r="G34" t="s">
+        <v>165</v>
+      </c>
+      <c r="H34" t="s">
         <v>247</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <v>3</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>237</v>
       </c>
@@ -2174,25 +2355,28 @@
         <v>8</v>
       </c>
       <c r="D35" t="s">
+        <v>260</v>
+      </c>
+      <c r="E35" t="s">
         <v>71</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>184</v>
       </c>
-      <c r="F35" t="s">
-        <v>165</v>
-      </c>
       <c r="G35" t="s">
+        <v>165</v>
+      </c>
+      <c r="H35" t="s">
         <v>86</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <v>3</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>242</v>
       </c>
@@ -2203,25 +2387,28 @@
         <v>8</v>
       </c>
       <c r="D36" t="s">
+        <v>260</v>
+      </c>
+      <c r="E36" t="s">
         <v>71</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" t="s">
         <v>184</v>
       </c>
-      <c r="F36" t="s">
-        <v>165</v>
-      </c>
       <c r="G36" t="s">
+        <v>165</v>
+      </c>
+      <c r="H36" t="s">
         <v>86</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>3</v>
       </c>
-      <c r="I36">
+      <c r="J36">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>129</v>
       </c>
@@ -2232,25 +2419,28 @@
         <v>8</v>
       </c>
       <c r="D37" t="s">
+        <v>260</v>
+      </c>
+      <c r="E37" t="s">
         <v>71</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>184</v>
       </c>
-      <c r="F37" t="s">
-        <v>165</v>
-      </c>
       <c r="G37" t="s">
+        <v>165</v>
+      </c>
+      <c r="H37" t="s">
         <v>86</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <v>3</v>
       </c>
-      <c r="I37">
+      <c r="J37">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>127</v>
       </c>
@@ -2261,25 +2451,28 @@
         <v>8</v>
       </c>
       <c r="D38" t="s">
+        <v>260</v>
+      </c>
+      <c r="E38" t="s">
         <v>64</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>181</v>
       </c>
-      <c r="F38" t="s">
-        <v>165</v>
-      </c>
       <c r="G38" t="s">
+        <v>165</v>
+      </c>
+      <c r="H38" t="s">
         <v>182</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <v>3</v>
       </c>
-      <c r="I38">
+      <c r="J38">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>131</v>
       </c>
@@ -2290,25 +2483,28 @@
         <v>8</v>
       </c>
       <c r="D39" t="s">
+        <v>260</v>
+      </c>
+      <c r="E39" t="s">
         <v>64</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>181</v>
       </c>
-      <c r="F39" t="s">
-        <v>165</v>
-      </c>
       <c r="G39" t="s">
+        <v>165</v>
+      </c>
+      <c r="H39" t="s">
         <v>182</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>3</v>
       </c>
-      <c r="I39">
+      <c r="J39">
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>187</v>
       </c>
@@ -2319,25 +2515,28 @@
         <v>8</v>
       </c>
       <c r="D40" t="s">
+        <v>260</v>
+      </c>
+      <c r="E40" t="s">
         <v>185</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
         <v>189</v>
       </c>
-      <c r="F40" t="s">
-        <v>165</v>
-      </c>
       <c r="G40" t="s">
+        <v>165</v>
+      </c>
+      <c r="H40" t="s">
         <v>191</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>3</v>
       </c>
-      <c r="I40">
+      <c r="J40">
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>193</v>
       </c>
@@ -2348,25 +2547,28 @@
         <v>8</v>
       </c>
       <c r="D41" t="s">
+        <v>260</v>
+      </c>
+      <c r="E41" t="s">
         <v>185</v>
       </c>
-      <c r="E41" t="s">
+      <c r="F41" t="s">
         <v>189</v>
       </c>
-      <c r="F41" t="s">
-        <v>165</v>
-      </c>
       <c r="G41" t="s">
+        <v>165</v>
+      </c>
+      <c r="H41" t="s">
         <v>191</v>
       </c>
-      <c r="H41">
+      <c r="I41">
         <v>3</v>
       </c>
-      <c r="I41">
+      <c r="J41">
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>188</v>
       </c>
@@ -2377,25 +2579,28 @@
         <v>8</v>
       </c>
       <c r="D42" t="s">
+        <v>260</v>
+      </c>
+      <c r="E42" t="s">
         <v>186</v>
       </c>
-      <c r="E42" t="s">
+      <c r="F42" t="s">
         <v>190</v>
       </c>
-      <c r="F42" t="s">
-        <v>165</v>
-      </c>
       <c r="G42" t="s">
+        <v>165</v>
+      </c>
+      <c r="H42" t="s">
         <v>192</v>
       </c>
-      <c r="H42">
+      <c r="I42">
         <v>3</v>
       </c>
-      <c r="I42">
+      <c r="J42">
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>194</v>
       </c>
@@ -2406,25 +2611,28 @@
         <v>8</v>
       </c>
       <c r="D43" t="s">
+        <v>260</v>
+      </c>
+      <c r="E43" t="s">
         <v>186</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
         <v>190</v>
       </c>
-      <c r="F43" t="s">
-        <v>165</v>
-      </c>
       <c r="G43" t="s">
+        <v>165</v>
+      </c>
+      <c r="H43" t="s">
         <v>192</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <v>3</v>
       </c>
-      <c r="I43">
+      <c r="J43">
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>128</v>
       </c>
@@ -2435,25 +2643,28 @@
         <v>8</v>
       </c>
       <c r="D44" t="s">
+        <v>260</v>
+      </c>
+      <c r="E44" t="s">
         <v>65</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>183</v>
       </c>
-      <c r="F44" t="s">
-        <v>165</v>
-      </c>
       <c r="G44" t="s">
+        <v>165</v>
+      </c>
+      <c r="H44" t="s">
         <v>81</v>
       </c>
-      <c r="H44">
+      <c r="I44">
         <v>3</v>
       </c>
-      <c r="I44">
+      <c r="J44">
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>99</v>
       </c>
@@ -2464,25 +2675,28 @@
         <v>11</v>
       </c>
       <c r="D45" t="s">
+        <v>261</v>
+      </c>
+      <c r="E45" t="s">
         <v>62</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>196</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>197</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>195</v>
       </c>
-      <c r="H45">
+      <c r="I45">
         <v>4</v>
       </c>
-      <c r="I45">
+      <c r="J45">
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>100</v>
       </c>
@@ -2493,25 +2707,28 @@
         <v>12</v>
       </c>
       <c r="D46" t="s">
+        <v>262</v>
+      </c>
+      <c r="E46" t="s">
         <v>73</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>199</v>
       </c>
-      <c r="F46" t="s">
-        <v>165</v>
-      </c>
       <c r="G46" t="s">
+        <v>165</v>
+      </c>
+      <c r="H46" t="s">
         <v>198</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>4</v>
       </c>
-      <c r="I46">
+      <c r="J46">
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>101</v>
       </c>
@@ -2522,25 +2739,28 @@
         <v>13</v>
       </c>
       <c r="D47" t="s">
+        <v>263</v>
+      </c>
+      <c r="E47" t="s">
         <v>61</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>201</v>
       </c>
-      <c r="F47" t="s">
-        <v>165</v>
-      </c>
       <c r="G47" t="s">
+        <v>165</v>
+      </c>
+      <c r="H47" t="s">
         <v>200</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <v>4</v>
       </c>
-      <c r="I47">
+      <c r="J47">
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>207</v>
       </c>
@@ -2551,25 +2771,28 @@
         <v>13</v>
       </c>
       <c r="D48" t="s">
+        <v>263</v>
+      </c>
+      <c r="E48" t="s">
         <v>61</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" t="s">
         <v>201</v>
       </c>
-      <c r="F48" t="s">
-        <v>165</v>
-      </c>
       <c r="G48" t="s">
+        <v>165</v>
+      </c>
+      <c r="H48" t="s">
         <v>200</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <v>4</v>
       </c>
-      <c r="I48">
+      <c r="J48">
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>102</v>
       </c>
@@ -2580,25 +2803,28 @@
         <v>13</v>
       </c>
       <c r="D49" t="s">
+        <v>263</v>
+      </c>
+      <c r="E49" t="s">
         <v>61</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
         <v>201</v>
       </c>
-      <c r="F49" t="s">
-        <v>165</v>
-      </c>
       <c r="G49" t="s">
+        <v>165</v>
+      </c>
+      <c r="H49" t="s">
         <v>200</v>
       </c>
-      <c r="H49">
+      <c r="I49">
         <v>4</v>
       </c>
-      <c r="I49">
+      <c r="J49">
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>203</v>
       </c>
@@ -2609,25 +2835,28 @@
         <v>13</v>
       </c>
       <c r="D50" t="s">
+        <v>263</v>
+      </c>
+      <c r="E50" t="s">
         <v>61</v>
       </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
         <v>201</v>
       </c>
-      <c r="F50" t="s">
-        <v>165</v>
-      </c>
       <c r="G50" t="s">
+        <v>165</v>
+      </c>
+      <c r="H50" t="s">
         <v>200</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <v>4</v>
       </c>
-      <c r="I50">
+      <c r="J50">
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>208</v>
       </c>
@@ -2638,25 +2867,28 @@
         <v>13</v>
       </c>
       <c r="D51" t="s">
+        <v>263</v>
+      </c>
+      <c r="E51" t="s">
         <v>202</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>205</v>
       </c>
-      <c r="F51" t="s">
-        <v>165</v>
-      </c>
       <c r="G51" t="s">
+        <v>165</v>
+      </c>
+      <c r="H51" t="s">
         <v>206</v>
       </c>
-      <c r="H51">
+      <c r="I51">
         <v>4</v>
       </c>
-      <c r="I51">
+      <c r="J51">
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>204</v>
       </c>
@@ -2667,25 +2899,28 @@
         <v>13</v>
       </c>
       <c r="D52" t="s">
+        <v>263</v>
+      </c>
+      <c r="E52" t="s">
         <v>202</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>205</v>
       </c>
-      <c r="F52" t="s">
-        <v>165</v>
-      </c>
       <c r="G52" t="s">
+        <v>165</v>
+      </c>
+      <c r="H52" t="s">
         <v>206</v>
       </c>
-      <c r="H52">
+      <c r="I52">
         <v>4</v>
       </c>
-      <c r="I52">
+      <c r="J52">
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>104</v>
       </c>
@@ -2696,25 +2931,28 @@
         <v>15</v>
       </c>
       <c r="D53" t="s">
+        <v>266</v>
+      </c>
+      <c r="E53" t="s">
         <v>58</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>209</v>
       </c>
-      <c r="F53" t="s">
-        <v>165</v>
-      </c>
       <c r="G53" t="s">
+        <v>165</v>
+      </c>
+      <c r="H53" t="s">
         <v>85</v>
       </c>
-      <c r="H53">
+      <c r="I53">
         <v>5</v>
       </c>
-      <c r="I53">
+      <c r="J53">
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>106</v>
       </c>
@@ -2725,25 +2963,28 @@
         <v>15</v>
       </c>
       <c r="D54" t="s">
+        <v>266</v>
+      </c>
+      <c r="E54" t="s">
         <v>58</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>209</v>
       </c>
-      <c r="F54" t="s">
-        <v>165</v>
-      </c>
       <c r="G54" t="s">
+        <v>165</v>
+      </c>
+      <c r="H54" t="s">
         <v>85</v>
       </c>
-      <c r="H54">
+      <c r="I54">
         <v>5</v>
       </c>
-      <c r="I54">
+      <c r="J54">
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>105</v>
       </c>
@@ -2754,25 +2995,28 @@
         <v>15</v>
       </c>
       <c r="D55" t="s">
+        <v>266</v>
+      </c>
+      <c r="E55" t="s">
         <v>58</v>
       </c>
-      <c r="E55" t="s">
+      <c r="F55" t="s">
         <v>209</v>
       </c>
-      <c r="F55" t="s">
-        <v>165</v>
-      </c>
       <c r="G55" t="s">
+        <v>165</v>
+      </c>
+      <c r="H55" t="s">
         <v>85</v>
       </c>
-      <c r="H55">
+      <c r="I55">
         <v>5</v>
       </c>
-      <c r="I55">
+      <c r="J55">
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>103</v>
       </c>
@@ -2783,25 +3027,28 @@
         <v>15</v>
       </c>
       <c r="D56" t="s">
+        <v>266</v>
+      </c>
+      <c r="E56" t="s">
         <v>58</v>
       </c>
-      <c r="E56" t="s">
+      <c r="F56" t="s">
         <v>209</v>
       </c>
-      <c r="F56" t="s">
-        <v>165</v>
-      </c>
       <c r="G56" t="s">
+        <v>165</v>
+      </c>
+      <c r="H56" t="s">
         <v>85</v>
       </c>
-      <c r="H56">
+      <c r="I56">
         <v>5</v>
       </c>
-      <c r="I56">
+      <c r="J56">
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>108</v>
       </c>
@@ -2812,25 +3059,28 @@
         <v>15</v>
       </c>
       <c r="D57" t="s">
+        <v>266</v>
+      </c>
+      <c r="E57" t="s">
         <v>58</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>209</v>
       </c>
-      <c r="F57" t="s">
-        <v>165</v>
-      </c>
       <c r="G57" t="s">
+        <v>165</v>
+      </c>
+      <c r="H57" t="s">
         <v>85</v>
       </c>
-      <c r="H57">
+      <c r="I57">
         <v>5</v>
       </c>
-      <c r="I57">
+      <c r="J57">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>107</v>
       </c>
@@ -2841,25 +3091,28 @@
         <v>15</v>
       </c>
       <c r="D58" t="s">
+        <v>266</v>
+      </c>
+      <c r="E58" t="s">
         <v>74</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>210</v>
       </c>
-      <c r="F58" t="s">
-        <v>165</v>
-      </c>
       <c r="G58" t="s">
+        <v>165</v>
+      </c>
+      <c r="H58" t="s">
         <v>211</v>
       </c>
-      <c r="H58">
+      <c r="I58">
         <v>5</v>
       </c>
-      <c r="I58">
+      <c r="J58">
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>253</v>
       </c>
@@ -2870,25 +3123,28 @@
         <v>16</v>
       </c>
       <c r="D59" t="s">
+        <v>267</v>
+      </c>
+      <c r="E59" t="s">
         <v>66</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>212</v>
       </c>
-      <c r="F59" t="s">
-        <v>165</v>
-      </c>
       <c r="G59" t="s">
+        <v>165</v>
+      </c>
+      <c r="H59" t="s">
         <v>82</v>
       </c>
-      <c r="H59">
+      <c r="I59">
         <v>5</v>
       </c>
-      <c r="I59">
+      <c r="J59">
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>109</v>
       </c>
@@ -2899,25 +3155,28 @@
         <v>20</v>
       </c>
       <c r="D60" t="s">
+        <v>264</v>
+      </c>
+      <c r="E60" t="s">
         <v>75</v>
       </c>
-      <c r="E60" t="s">
+      <c r="F60" t="s">
         <v>213</v>
       </c>
-      <c r="F60" t="s">
-        <v>165</v>
-      </c>
       <c r="G60" t="s">
+        <v>165</v>
+      </c>
+      <c r="H60" t="s">
         <v>88</v>
       </c>
-      <c r="H60">
+      <c r="I60">
         <v>5</v>
       </c>
-      <c r="I60">
+      <c r="J60">
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>110</v>
       </c>
@@ -2928,25 +3187,28 @@
         <v>20</v>
       </c>
       <c r="D61" t="s">
+        <v>264</v>
+      </c>
+      <c r="E61" t="s">
         <v>75</v>
       </c>
-      <c r="E61" t="s">
+      <c r="F61" t="s">
         <v>250</v>
       </c>
-      <c r="F61" t="s">
-        <v>165</v>
-      </c>
       <c r="G61" t="s">
+        <v>165</v>
+      </c>
+      <c r="H61" t="s">
         <v>214</v>
       </c>
-      <c r="H61">
+      <c r="I61">
         <v>5</v>
       </c>
-      <c r="I61">
+      <c r="J61">
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>228</v>
       </c>
@@ -2957,25 +3219,28 @@
         <v>20</v>
       </c>
       <c r="D62" t="s">
+        <v>264</v>
+      </c>
+      <c r="E62" t="s">
         <v>230</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="s">
         <v>234</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>217</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>232</v>
       </c>
-      <c r="H62">
+      <c r="I62">
         <v>5</v>
       </c>
-      <c r="I62">
+      <c r="J62">
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>112</v>
       </c>
@@ -2986,25 +3251,28 @@
         <v>25</v>
       </c>
       <c r="D63" t="s">
+        <v>265</v>
+      </c>
+      <c r="E63" t="s">
         <v>55</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>225</v>
       </c>
-      <c r="F63" t="s">
-        <v>165</v>
-      </c>
       <c r="G63" t="s">
+        <v>165</v>
+      </c>
+      <c r="H63" t="s">
         <v>226</v>
       </c>
-      <c r="H63">
+      <c r="I63">
         <v>6</v>
       </c>
-      <c r="I63">
+      <c r="J63">
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>111</v>
       </c>
@@ -3015,25 +3283,28 @@
         <v>25</v>
       </c>
       <c r="D64" t="s">
+        <v>265</v>
+      </c>
+      <c r="E64" t="s">
         <v>55</v>
       </c>
-      <c r="E64" t="s">
+      <c r="F64" t="s">
         <v>215</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
         <v>217</v>
       </c>
-      <c r="G64" t="s">
+      <c r="H64" t="s">
         <v>216</v>
       </c>
-      <c r="H64">
+      <c r="I64">
         <v>6</v>
       </c>
-      <c r="I64">
+      <c r="J64">
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>219</v>
       </c>
@@ -3044,25 +3315,28 @@
         <v>25</v>
       </c>
       <c r="D65" t="s">
+        <v>265</v>
+      </c>
+      <c r="E65" t="s">
         <v>55</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>224</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>197</v>
       </c>
-      <c r="G65" t="s">
+      <c r="H65" t="s">
         <v>221</v>
       </c>
-      <c r="H65">
+      <c r="I65">
         <v>6</v>
       </c>
-      <c r="I65">
+      <c r="J65">
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>220</v>
       </c>
@@ -3073,31 +3347,36 @@
         <v>25</v>
       </c>
       <c r="D66" t="s">
+        <v>265</v>
+      </c>
+      <c r="E66" t="s">
         <v>218</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>223</v>
       </c>
-      <c r="F66" t="s">
-        <v>165</v>
-      </c>
       <c r="G66" t="s">
+        <v>165</v>
+      </c>
+      <c r="H66" t="s">
         <v>222</v>
       </c>
-      <c r="H66">
+      <c r="I66">
         <v>6</v>
       </c>
-      <c r="I66">
+      <c r="J66">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I66" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G67">
+  <autoFilter ref="A1:J66" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState ref="A2:H67">
     <sortCondition ref="C2:C67"/>
-    <sortCondition ref="D2:D67"/>
+    <sortCondition ref="E2:E67"/>
     <sortCondition ref="B2:B67"/>
   </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>